--- a/data/indicadores/05_05_01_05_acm.xlsx
+++ b/data/indicadores/05_05_01_05_acm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\ods_paolo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9E6822A-DE53-49ED-9308-255FFC25057D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F41F3193-7AB8-4AD4-82B2-112905E7CBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{1F0CCE29-C528-4204-AA1E-F32404105712}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{1F0CCE29-C528-4204-AA1E-F32404105712}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos procesados" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2134" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="508">
   <si>
     <t>Depart</t>
   </si>
@@ -24120,7 +24120,7 @@
   <sheetPr>
     <tabColor rgb="FFAF2738"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -24261,6 +24261,34 @@
       </c>
       <c r="D10" s="10">
         <v>55.000000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C11" s="10">
+        <v>54.166666666666664</v>
+      </c>
+      <c r="D11" s="10">
+        <v>56.000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C12" s="10">
+        <v>49.48352188883424</v>
+      </c>
+      <c r="D12" s="10">
+        <v>51.963746223564954</v>
       </c>
     </row>
   </sheetData>
